--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_story_talk_info[故事对话信息].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_story_talk_info[故事对话信息].xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>id</t>
   </si>
@@ -61,13 +61,25 @@
     <t>介绍基地</t>
   </si>
   <si>
+    <t>介绍-出场</t>
+  </si>
+  <si>
+    <t>介绍-进度</t>
+  </si>
+  <si>
+    <t>介绍-上场魔物</t>
+  </si>
+  <si>
+    <t>介绍-魔量</t>
+  </si>
+  <si>
+    <t>介绍-清除按钮</t>
+  </si>
+  <si>
+    <t>魔晶说明</t>
+  </si>
+  <si>
     <t>介绍传送门</t>
-  </si>
-  <si>
-    <t>忠心-战斗说明2</t>
-  </si>
-  <si>
-    <t>忠心-拾晶说明</t>
   </si>
 </sst>
 </file>
@@ -471,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,7 +539,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="B4" s="0">
         <v>1</v>
@@ -536,7 +548,7 @@
         <v>10001</v>
       </c>
       <c r="D4" s="0">
-        <v>1</v>
+        <v>1001</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>12</v>
@@ -544,7 +556,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>2</v>
+        <v>1002</v>
       </c>
       <c r="B5" s="0">
         <v>1</v>
@@ -553,7 +565,7 @@
         <v>10001</v>
       </c>
       <c r="D5" s="0">
-        <v>2</v>
+        <v>1002</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>13</v>
@@ -561,7 +573,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>3</v>
+        <v>1003</v>
       </c>
       <c r="B6" s="0">
         <v>1</v>
@@ -570,7 +582,7 @@
         <v>10001</v>
       </c>
       <c r="D6" s="0">
-        <v>3</v>
+        <v>1003</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>14</v>
@@ -578,7 +590,7 @@
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>4</v>
+        <v>2001</v>
       </c>
       <c r="B7" s="0">
         <v>2</v>
@@ -587,7 +599,7 @@
         <v>10001</v>
       </c>
       <c r="D7" s="0">
-        <v>4</v>
+        <v>2001</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>15</v>
@@ -595,16 +607,16 @@
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>5</v>
+        <v>2002</v>
       </c>
       <c r="B8" s="0">
         <v>2</v>
       </c>
       <c r="C8" s="0">
-        <v>3</v>
+        <v>10001</v>
       </c>
       <c r="D8" s="0">
-        <v>5</v>
+        <v>2002</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>16</v>
@@ -612,19 +624,87 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>6</v>
+        <v>2003</v>
       </c>
       <c r="B9" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="0">
-        <v>3</v>
+        <v>10001</v>
       </c>
       <c r="D9" s="0">
-        <v>6</v>
+        <v>2003</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>2004</v>
+      </c>
+      <c r="B10" s="0">
+        <v>2</v>
+      </c>
+      <c r="C10" s="0">
+        <v>10001</v>
+      </c>
+      <c r="D10" s="0">
+        <v>2004</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>2005</v>
+      </c>
+      <c r="B11" s="0">
+        <v>2</v>
+      </c>
+      <c r="C11" s="0">
+        <v>10001</v>
+      </c>
+      <c r="D11" s="0">
+        <v>2005</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>3001</v>
+      </c>
+      <c r="B12" s="0">
+        <v>3</v>
+      </c>
+      <c r="C12" s="0">
+        <v>10001</v>
+      </c>
+      <c r="D12" s="0">
+        <v>3001</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>1004</v>
+      </c>
+      <c r="B13" s="0">
+        <v>1</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0</v>
+      </c>
+      <c r="D13" s="0">
+        <v>1004</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
